--- a/healthcare_forms/021_dental_appointment_reservation_form--healthcare_forms.xlsx
+++ b/healthcare_forms/021_dental_appointment_reservation_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'doctor_1',_'label':_'doctor_1'}</t>
+          <t>doctor_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'Doctor 1', 'label': 'Doctor 1'}</t>
+          <t>Doctor 1</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'doctor_2',_'label':_'doctor_2'}</t>
+          <t>doctor_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'Doctor 2', 'label': 'Doctor 2'}</t>
+          <t>Doctor 2</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'doctor_3',_'label':_'doctor_3'}</t>
+          <t>doctor_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'Doctor 3', 'label': 'Doctor 3'}</t>
+          <t>Doctor 3</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'cash',_'label':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'Cash', 'label': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'credit_card',_'label':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'Credit Card', 'label': 'Credit Card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'insurance',_'label':_'insurance'}</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'Insurance', 'label': 'Insurance'}</t>
+          <t>Insurance</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'paid',_'label':_'paid'}</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'Paid', 'label': 'Paid'}</t>
+          <t>Paid</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'unpaid',_'label':_'unpaid'}</t>
+          <t>unpaid</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'Unpaid', 'label': 'Unpaid'}</t>
+          <t>Unpaid</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'partially_paid',_'label':_'partially_paid'}</t>
+          <t>partially_paid</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'Partially Paid', 'label': 'Partially Paid'}</t>
+          <t>Partially Paid</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'general_dentistry',_'label':_'general_dentistry'}</t>
+          <t>general_dentistry</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'General Dentistry', 'label': 'General Dentistry'}</t>
+          <t>General Dentistry</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'orthodontics',_'label':_'orthodontics'}</t>
+          <t>orthodontics</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'Orthodontics', 'label': 'Orthodontics'}</t>
+          <t>Orthodontics</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'oral_surgery',_'label':_'oral_surgery'}</t>
+          <t>oral_surgery</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'Oral Surgery', 'label': 'Oral Surgery'}</t>
+          <t>Oral Surgery</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'scheduled',_'label':_'scheduled'}</t>
+          <t>scheduled</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'Scheduled', 'label': 'Scheduled'}</t>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'name':_'confirmed',_'label':_'confirmed'}</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'name': 'Confirmed', 'label': 'Confirmed'}</t>
+          <t>Confirmed</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'name':_'cancelled',_'label':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'name': 'Cancelled', 'label': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'name':_'morning',_'label':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'name': 'Morning', 'label': 'Morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'name':_'afternoon',_'label':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'name': 'Afternoon', 'label': 'Afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'name':_'evening',_'label':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'name': 'Evening', 'label': 'Evening'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
